--- a/next-app/data/works_master.xlsx
+++ b/next-app/data/works_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\portfolio\next-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D486B1C6-5F58-4C9D-A2B2-70C2E611119A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{192B80D9-CA70-442A-854D-5EE5F8968F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -1951,11 +1951,6 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B33" s="2">
-        <v>9</v>
-      </c>
-    </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>35</v>

--- a/next-app/data/works_master.xlsx
+++ b/next-app/data/works_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\portfolio\next-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{192B80D9-CA70-442A-854D-5EE5F8968F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC914D9-0261-499D-BFAB-C3933EBFB8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5472" yWindow="1752" windowWidth="15612" windowHeight="9960" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">Fleet!$A$2:$H$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">GENERATIONS!$A$2:$H$36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'PSYCHIC FEVER'!$A$2:$H$37</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">ポートフォリオ!$A$2:$H$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">ポートフォリオ!$A$2:$H$32</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">社長の選択!$A$2:$H$38</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="226">
   <si>
     <t>アバターサービスを拡張した新コンテンツ</t>
   </si>
@@ -522,61 +522,19 @@
     <t>ポートフォリオ</t>
   </si>
   <si>
-    <t>フリーランス向けポートフォリオサイト</t>
-  </si>
-  <si>
     <t>portfolio</t>
   </si>
   <si>
     <t>https://github.com/hiratsuka-r/portfolio</t>
   </si>
   <si>
-    <t>個人制作ポートフォリオサイト</t>
-  </si>
-  <si>
     <t>ポートフォリオサイト</t>
   </si>
   <si>
-    <t>2025年</t>
-  </si>
-  <si>
-    <t>企画・設計・実装</t>
-  </si>
-  <si>
     <t>個人制作</t>
   </si>
   <si>
-    <t>企画、デザイン、フロントエンド</t>
-  </si>
-  <si>
     <t>自身のプロフィール、スキル、制作物を紹介するポートフォリオサイトです。閲覧者が経歴と制作実績を確認しやすいよう、情報をセクションごとに整理しています。</t>
-  </si>
-  <si>
-    <t>・Works一覧・詳細モーダルの設計・実装</t>
-  </si>
-  <si>
-    <t>・サイト構成の設計</t>
-  </si>
-  <si>
-    <t>・レスポンシブUIの設計・実装</t>
-  </si>
-  <si>
-    <t>・既存スタイルの改修・保守</t>
-  </si>
-  <si>
-    <t>・PC・タブレット・スマートフォンでの閲覧に対応</t>
-  </si>
-  <si>
-    <t>・制作物の一覧から詳細情報へスムーズに遷移できるUIを実装</t>
-  </si>
-  <si>
-    <t>・制作物の追加・更新をデータ変更中心で行える構成とし、保守性を向上</t>
-  </si>
-  <si>
-    <t>HTML / JavaScript / SCSS</t>
-  </si>
-  <si>
-    <t>GitHub / Gulp</t>
   </si>
   <si>
     <t>既存のアバターサービスを拡張し、4つのモバイルサイトと連携した「MEMBER BIRTHDAY PARTY」の新コンテンツ開発に携わりました。複数サイト間でデータ連携が発生する構成に対応し、連携された情報に応じてサイト名やカラーなどのUI・デザインを切り替えるフロントエンド実装を担当しました。</t>
@@ -749,6 +707,59 @@
   </si>
   <si>
     <t>/portfolio/img/works/portfolio.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GitHub / GitHub Copilot</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Next.js / TypeScript / SCSS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>担当内容</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GitHub Copilot</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企画、設計、デザイン、実装</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・PC・タブレット・スマートフォンでの閲覧に対応 </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・制作物の一覧から詳細情報へスムーズに遷移できるUIを実装 </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・制作物の追加・更新をデータ変更中心で行える構成とし、 保守性を向上</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロフィール・制作実績ポートフォリオ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポートフォリオ制作</t>
+    <rPh sb="7" eb="9">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要件定義～公開</t>
+    <rPh sb="0" eb="4">
+      <t>ヨウケンテイギ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウカイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1255,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultColWidth="24" defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
@@ -1270,7 +1281,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
-        <v>160</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1286,7 +1297,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
@@ -1294,7 +1305,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
@@ -1302,7 +1313,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
@@ -1310,7 +1321,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>163</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
@@ -1337,7 +1348,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
@@ -1350,9 +1361,7 @@
       <c r="A15" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>165</v>
-      </c>
+      <c r="B15" s="6"/>
     </row>
     <row r="16" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
@@ -1365,7 +1374,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>166</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
@@ -1394,7 +1403,7 @@
         <v>30</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
@@ -1402,7 +1411,7 @@
         <v>32</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>168</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -1412,76 +1421,60 @@
     </row>
     <row r="25" spans="1:2" ht="26.4" x14ac:dyDescent="0.2">
       <c r="B25" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
-      <c r="B27" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
-      <c r="B28" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
-      <c r="B29" s="3" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
-      <c r="B30" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="10" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
+      <c r="B26" s="3"/>
+    </row>
+    <row r="27" spans="1:2" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.2">
+      <c r="A27" s="12" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="10" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
+      <c r="B31" s="3" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="B32" s="3" t="s">
-        <v>174</v>
+        <v>222</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
-      <c r="B33" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
-      <c r="B34" s="3" t="s">
-        <v>176</v>
+      <c r="B33" s="3"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
-      <c r="B35" s="3"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
-      <c r="A37" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
-      <c r="A38" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>178</v>
+      <c r="B36" s="6" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -1492,7 +1485,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultColWidth="85" defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" style="2" customWidth="1"/>
@@ -1531,7 +1524,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -1654,7 +1647,7 @@
     </row>
     <row r="27" spans="1:2" ht="26.4" x14ac:dyDescent="0.2">
       <c r="B27" s="4" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
@@ -1710,7 +1703,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
@@ -1740,6 +1733,14 @@
       </c>
       <c r="B43" s="7" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -1761,7 +1762,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -1790,7 +1791,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -1848,7 +1849,7 @@
         <v>18</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -1912,7 +1913,7 @@
     </row>
     <row r="25" spans="1:2" ht="52.8" x14ac:dyDescent="0.2">
       <c r="B25" s="4" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -1923,7 +1924,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" s="19" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
@@ -1938,7 +1939,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B30" s="19" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -2056,7 +2057,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -2085,7 +2086,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
@@ -2211,7 +2212,7 @@
         <v>32</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
@@ -2222,7 +2223,7 @@
     </row>
     <row r="26" spans="1:2" ht="39.6" x14ac:dyDescent="0.2">
       <c r="B26" s="3" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
@@ -2233,32 +2234,32 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -2268,17 +2269,17 @@
     </row>
     <row r="35" spans="1:2" ht="13.8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
@@ -2350,7 +2351,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -2374,7 +2375,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -2494,7 +2495,7 @@
     </row>
     <row r="25" spans="1:2" ht="26.4" x14ac:dyDescent="0.2">
       <c r="B25" s="4" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -2530,7 +2531,7 @@
     </row>
     <row r="32" spans="1:2" ht="26.4" x14ac:dyDescent="0.2">
       <c r="B32" s="4" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -2602,7 +2603,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -2626,7 +2627,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
@@ -2740,7 +2741,7 @@
         <v>32</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
@@ -2751,7 +2752,7 @@
     </row>
     <row r="25" spans="1:2" ht="26.4" x14ac:dyDescent="0.2">
       <c r="B25" s="4" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
@@ -2763,7 +2764,7 @@
     <row r="27" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="4" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
@@ -2785,7 +2786,7 @@
     </row>
     <row r="31" spans="1:2" ht="26.4" x14ac:dyDescent="0.2">
       <c r="B31" s="4" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
@@ -2872,7 +2873,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -2896,7 +2897,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -3016,7 +3017,7 @@
     </row>
     <row r="25" spans="1:2" ht="39.6" x14ac:dyDescent="0.2">
       <c r="B25" s="4" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -3037,12 +3038,12 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -3052,12 +3053,12 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -3156,7 +3157,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -3209,7 +3210,7 @@
         <v>16</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -3241,7 +3242,7 @@
         <v>24</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -3285,7 +3286,7 @@
     </row>
     <row r="25" spans="1:2" ht="26.4" x14ac:dyDescent="0.2">
       <c r="B25" s="4" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -3326,12 +3327,12 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -3422,7 +3423,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -3475,7 +3476,7 @@
         <v>16</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -3491,7 +3492,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -3549,7 +3550,7 @@
     </row>
     <row r="25" spans="1:2" ht="39.6" x14ac:dyDescent="0.2">
       <c r="B25" s="4" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">

--- a/next-app/data/works_master.xlsx
+++ b/next-app/data/works_master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\portfolio\next-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC914D9-0261-499D-BFAB-C3933EBFB8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC2A908-7773-4C7B-A5F4-CB9F0820E66F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5472" yWindow="1752" windowWidth="15612" windowHeight="9960" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'EXILE mobile - MBP'!$A$2:$H$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'EXILE TETSUYA'!$A$2:$H$38</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'EXILE TRIBE mobile'!$A$2:$H$45</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Fleet!$A$2:$H$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Fleet!$A$2:$H$41</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">GENERATIONS!$A$2:$H$36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'PSYCHIC FEVER'!$A$2:$H$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">ポートフォリオ!$A$2:$H$32</definedName>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="229">
   <si>
     <t>アバターサービスを拡張した新コンテンツ</t>
   </si>
@@ -51,9 +51,6 @@
     <t>ID</t>
   </si>
   <si>
-    <t>exile-member-birthday-party</t>
-  </si>
-  <si>
     <t>画像</t>
   </si>
   <si>
@@ -216,9 +213,6 @@
     <t>車両動態管理システム・管理画面</t>
   </si>
   <si>
-    <t>smart-construction-fleet</t>
-  </si>
-  <si>
     <t>https://jp.smartconstruction.com/smart-construction-fleet</t>
   </si>
   <si>
@@ -243,30 +237,6 @@
     <t>新規開発、既存保守、フロントエンド</t>
   </si>
   <si>
-    <t>・車両動態管理システムの管理画面におけるフロントエンド開発・保守</t>
-  </si>
-  <si>
-    <t>・既存機能の改修および利用現場からの要望を踏まえた機能改善</t>
-  </si>
-  <si>
-    <t>・ダンプの積み下ろし工程を管理する予実管理機能の新規開発</t>
-  </si>
-  <si>
-    <t>・走行履歴・レポート・各種表示機能など、管理画面全体に関わる機能改修</t>
-  </si>
-  <si>
-    <t>・REST APIの改修対応などバックエンド開発の補佐</t>
-  </si>
-  <si>
-    <t>・詳細設計から実装・テストまでの下流工程を担当</t>
-  </si>
-  <si>
-    <t>・ダンプの積み下ろし回数や移動土量などを確認できる予実管理機能を新規開発</t>
-  </si>
-  <si>
-    <t>・船舶や低速車両が中心となる現場からの要望を受け、走行履歴画面の速度帯・表示色を切り替えられる機能を追加</t>
-  </si>
-  <si>
     <t>Next.js / TypeScript</t>
   </si>
   <si>
@@ -282,9 +252,6 @@
     <t>マイページ・アバターサービス</t>
   </si>
   <si>
-    <t>exile-tribe-mypage</t>
-  </si>
-  <si>
     <t>https://m.tribe-m.jp/common/mypage/tutorial/mypage/index</t>
   </si>
   <si>
@@ -330,9 +297,6 @@
     <t>PSYCHIC FEVER</t>
   </si>
   <si>
-    <t>psychic-fever</t>
-  </si>
-  <si>
     <t>https://m.tribe-m.jp/Artist/index/262</t>
   </si>
   <si>
@@ -357,9 +321,6 @@
     <t>GENERATIONS</t>
   </si>
   <si>
-    <t>generations</t>
-  </si>
-  <si>
     <t>https://m.tribe-m.jp/artist/index/37</t>
   </si>
   <si>
@@ -384,9 +345,6 @@
     <t>EXILE TETSUYA</t>
   </si>
   <si>
-    <t>exile-tetsuya</t>
-  </si>
-  <si>
     <t>https://m.ex-m.jp/artist/index/11</t>
   </si>
   <si>
@@ -405,9 +363,6 @@
     <t>オーナー経営者さま限定カンファレンス</t>
   </si>
   <si>
-    <t>shacho-no-sentaku</t>
-  </si>
-  <si>
     <t>https://www.nihon-ma.co.jp/seminar/sentaku2024/</t>
   </si>
   <si>
@@ -459,9 +414,6 @@
     <t>動画配信型LMS・CMS</t>
   </si>
   <si>
-    <t>adminttv-webinar</t>
-  </si>
-  <si>
     <t>https://www.digital-cruise.co.jp/webinar/</t>
   </si>
   <si>
@@ -566,13 +518,6 @@
   </si>
   <si>
     <t>・複数のプロトタイプをデザイナー・運営側に確認して合意を得た上で実装を進め、新規サービスの仕様を固めながら開発</t>
-  </si>
-  <si>
-    <t>建設現場における車両・建設機械の位置情報や稼働状況を管理する車両動態管理システム。施工・施工管理フェーズで利用される管理画面のフロントエンド開発を担当しました。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・重量表示をキログラム・ポンドのみからトンにも対応し、レポート機能では日・週・月単位に限定されていた期間指定を任意の期間で絞り込めるよう拡張</t>
   </si>
   <si>
     <t>芸能系モバイルファンサイトの関連サイトとして、アーティストページのリニューアルに携わりました。デザイナーが制作したアーティストの世界観をもとに、フロントエンド側で動きや演出を実装しました。</t>
@@ -719,10 +664,6 @@
   </si>
   <si>
     <t>担当内容</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>GitHub Copilot</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -760,6 +701,90 @@
     <rPh sb="5" eb="7">
       <t>コウカイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>scfleet</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tr-mypage</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ex-birthday</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tr-generations</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tr-psychic-fever</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ex-tetsuya</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>m-and-a</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>webinar</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GitHub Copilot / Microsoft 365 Copilot</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>建設現場における車両・建設機械の位置情報や稼働状況を管理する車両動態管理システム。施工・施工管理フェーズで利用される管理画面の開発・保守を担当しました。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・詳細設計から実装・テスト・レビューまでの開発工程を担当</t>
+  </si>
+  <si>
+    <t>・ダンプの積み下ろし回数や移動土量などを確認できる予実管理機能を新規開発</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・船舶や低速車両が中心となる現場からの要望を受け、走行履歴画面で速度帯・表示色を切り替えられる機能を追加</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・重量表示をキログラム・ポンドに加えてトンにも対応</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・レポート機能の期間指定を日・週・月単位から任意期間に拡張</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・走行履歴・レポート・各種表示機能など、既存管理画面の機能改善を実施</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・管理画面のフロントエンド開発・保守</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・REST APIの改修など、バックエンド開発の対応</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・定例会での顧客との要件・仕様のすり合わせ</t>
+  </si>
+  <si>
+    <t>・AIを活用した開発手法を取り入れ、要件整理から実装・レビューまで一貫して対応</t>
+  </si>
+  <si>
+    <t>・顧客から事前にご要望を伺い、要件・仕様を整理・提案</t>
+  </si>
+  <si>
+    <t>新規開発、既存保守、フロントエンド、バックエンド</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1221,41 +1246,41 @@
   <sheetData>
     <row r="1" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>48</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1276,12 +1301,12 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1297,95 +1322,95 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1"/>
     </row>
     <row r="10" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>11</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" s="1"/>
     </row>
     <row r="15" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="6"/>
     </row>
     <row r="16" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="1"/>
     </row>
     <row r="17" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="1"/>
     </row>
     <row r="19" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1"/>
     </row>
@@ -1395,33 +1420,33 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>219</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="26.4" x14ac:dyDescent="0.2">
       <c r="B25" s="3" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
@@ -1429,28 +1454,28 @@
     </row>
     <row r="27" spans="1:2" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="28" spans="1:2" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.2"/>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="B31" s="3" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="B32" s="3" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
@@ -1458,23 +1483,23 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -1485,7 +1510,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultColWidth="85" defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" style="2" customWidth="1"/>
@@ -1495,12 +1520,12 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1516,102 +1541,102 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>58</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>11</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -1620,127 +1645,137 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>66</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="7"/>
     </row>
     <row r="27" spans="1:2" ht="26.4" x14ac:dyDescent="0.2">
       <c r="B27" s="4" t="s">
-        <v>175</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="4"/>
+    </row>
+    <row r="29" spans="1:2" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="12" t="s">
         <v>34</v>
-      </c>
-      <c r="B28" s="4"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B29" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B30" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B31" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B32" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B33" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B35" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B36" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
-        <v>74</v>
+        <v>218</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>176</v>
+        <v>219</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B39" s="2" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="11" t="s">
-        <v>36</v>
+      <c r="B40" s="2" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>76</v>
+      <c r="B41" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>218</v>
+      <c r="A44" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -1762,12 +1797,12 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1783,102 +1818,102 @@
         <v>2</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>80</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>7</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>9</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>11</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="18" t="s">
         <v>14</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="18" t="s">
         <v>20</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -1887,99 +1922,99 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="18" t="s">
         <v>30</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="52.8" x14ac:dyDescent="0.2">
       <c r="B25" s="4" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="17"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" s="19" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B28" s="19" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B29" s="19" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B30" s="19" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B31" s="19" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B32" s="19" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
@@ -1987,55 +2022,55 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B42" s="18" t="s">
         <v>37</v>
-      </c>
-      <c r="B42" s="18" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="B43" s="18" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="11" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="18" t="s">
         <v>41</v>
-      </c>
-      <c r="B45" s="18" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" s="18" t="s">
         <v>43</v>
-      </c>
-      <c r="B46" s="18" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2057,7 +2092,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -2078,116 +2113,116 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>3</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>5</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>7</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>9</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>11</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
@@ -2196,135 +2231,135 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="6"/>
     </row>
     <row r="26" spans="1:2" ht="39.6" x14ac:dyDescent="0.2">
       <c r="B26" s="3" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="3"/>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="13.8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A42" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A43" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>43</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A44" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -2346,12 +2381,12 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -2367,99 +2402,99 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>105</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>9</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>11</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>14</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -2468,115 +2503,115 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>30</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="7"/>
     </row>
     <row r="25" spans="1:2" ht="26.4" x14ac:dyDescent="0.2">
       <c r="B25" s="4" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="4"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="26.4" x14ac:dyDescent="0.2">
       <c r="B32" s="4" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -2598,12 +2633,12 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -2619,104 +2654,104 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>96</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>7</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>9</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>11</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" s="1"/>
     </row>
     <row r="15" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="1"/>
     </row>
     <row r="19" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -2724,81 +2759,81 @@
     </row>
     <row r="21" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>30</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="7"/>
     </row>
     <row r="25" spans="1:2" ht="26.4" x14ac:dyDescent="0.2">
       <c r="B25" s="4" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="4"/>
     </row>
     <row r="27" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="4" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="4" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="B29" s="4" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="4"/>
     </row>
     <row r="31" spans="1:2" ht="26.4" x14ac:dyDescent="0.2">
       <c r="B31" s="4" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="4" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="4" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
@@ -2806,47 +2841,47 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>43</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -2868,12 +2903,12 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -2889,99 +2924,99 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>114</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>9</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>11</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>14</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -2990,75 +3025,75 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>30</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="7"/>
     </row>
     <row r="25" spans="1:2" ht="39.6" x14ac:dyDescent="0.2">
       <c r="B25" s="4" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="4"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -3066,47 +3101,47 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -3128,12 +3163,12 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -3149,108 +3184,108 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>121</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>11</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -3259,80 +3294,80 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="7"/>
     </row>
     <row r="25" spans="1:2" ht="26.4" x14ac:dyDescent="0.2">
       <c r="B25" s="4" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="4"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -3340,39 +3375,39 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -3394,12 +3429,12 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -3415,106 +3450,106 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>139</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>11</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="19"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -3523,95 +3558,95 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="7"/>
     </row>
     <row r="25" spans="1:2" ht="39.6" x14ac:dyDescent="0.2">
       <c r="B25" s="4" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="4"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="26.4" x14ac:dyDescent="0.2">
       <c r="B36" s="4" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="26.4" x14ac:dyDescent="0.2">
       <c r="B37" s="4" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
@@ -3619,55 +3654,55 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="11" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
